--- a/Configs/Localization/本地化.xlsx
+++ b/Configs/Localization/本地化.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12790" activeTab="1"/>
+    <workbookView windowWidth="25600" windowHeight="12790"/>
   </bookViews>
   <sheets>
     <sheet name="ChineseSimplified" sheetId="1" r:id="rId1"/>
@@ -85,22 +85,22 @@
     <t>值</t>
   </si>
   <si>
-    <t>ClickBlock</t>
-  </si>
-  <si>
-    <t>点击块</t>
+    <t>BulletShoot</t>
+  </si>
+  <si>
+    <t>弹幕射击</t>
   </si>
   <si>
     <t>Demo</t>
   </si>
   <si>
-    <t>测试版</t>
-  </si>
-  <si>
-    <t>Click The Blocks!</t>
-  </si>
-  <si>
-    <t>GGF Demo Game</t>
+    <t>戈多游戏框架Demo</t>
+  </si>
+  <si>
+    <t>The BulletShoot</t>
+  </si>
+  <si>
+    <t>Godot GameFrameWork Demo Game</t>
   </si>
 </sst>
 </file>

--- a/Configs/Localization/本地化.xlsx
+++ b/Configs/Localization/本地化.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="22">
   <si>
     <t>##var</t>
   </si>
@@ -95,6 +95,18 @@
   </si>
   <si>
     <t>戈多游戏框架Demo</t>
+  </si>
+  <si>
+    <t>MainForm.Score</t>
+  </si>
+  <si>
+    <t>分数:</t>
+  </si>
+  <si>
+    <t>MainForm.Timer</t>
+  </si>
+  <si>
+    <t>计时:</t>
   </si>
   <si>
     <t>The BulletShoot</t>
@@ -1383,6 +1395,15 @@
       <c r="N7" s="13"/>
     </row>
     <row r="8" spans="1:36">
+      <c r="B8">
+        <v>3</v>
+      </c>
+      <c r="C8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" t="s">
+        <v>17</v>
+      </c>
       <c r="H8" s="12"/>
       <c r="J8" s="12"/>
       <c r="L8" s="12"/>
@@ -1390,6 +1411,15 @@
       <c r="N8" s="13"/>
     </row>
     <row r="9" spans="1:36">
+      <c r="B9">
+        <v>4</v>
+      </c>
+      <c r="C9" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" t="s">
+        <v>19</v>
+      </c>
       <c r="H9" s="12"/>
       <c r="J9" s="12"/>
       <c r="L9" s="12"/>
@@ -1534,7 +1564,7 @@
         <v>12</v>
       </c>
       <c r="D6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1545,7 +1575,7 @@
         <v>14</v>
       </c>
       <c r="D7" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/Localization/本地化.xlsx
+++ b/Configs/Localization/本地化.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12790"/>
+    <workbookView windowWidth="25600" windowHeight="12790" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="ChineseSimplified" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="27">
   <si>
     <t>##var</t>
   </si>
@@ -85,16 +85,22 @@
     <t>值</t>
   </si>
   <si>
-    <t>BulletShoot</t>
-  </si>
-  <si>
-    <t>弹幕射击</t>
-  </si>
-  <si>
-    <t>Demo</t>
-  </si>
-  <si>
-    <t>戈多游戏框架Demo</t>
+    <t>MonsterSurviver</t>
+  </si>
+  <si>
+    <t>怪物幸存者</t>
+  </si>
+  <si>
+    <t>MoveRule</t>
+  </si>
+  <si>
+    <t>WASD移动角色</t>
+  </si>
+  <si>
+    <t>StartGame</t>
+  </si>
+  <si>
+    <t>开始游戏</t>
   </si>
   <si>
     <t>MainForm.Score</t>
@@ -109,10 +115,19 @@
     <t>计时:</t>
   </si>
   <si>
-    <t>The BulletShoot</t>
-  </si>
-  <si>
-    <t>Godot GameFrameWork Demo Game</t>
+    <t>Monster Surviver</t>
+  </si>
+  <si>
+    <t>WASD To Move Character</t>
+  </si>
+  <si>
+    <t>Start</t>
+  </si>
+  <si>
+    <t>Score:</t>
+  </si>
+  <si>
+    <t>Timer:</t>
   </si>
 </sst>
 </file>
@@ -780,6 +795,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="22" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="23" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="22" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="23" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="22" applyBorder="1" applyAlignment="1">
@@ -799,10 +818,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="23" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1125,7 +1140,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AJ15"/>
+  <dimension ref="A1:AJ16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="9.225" customWidth="1"/>
@@ -1144,7 +1159,7 @@
     <col min="14" max="14" width="5.13333333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="3" customFormat="1" spans="1:36">
+    <row r="1" s="5" customFormat="1" spans="1:36">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1165,9 +1180,9 @@
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
-      <c r="M1" s="5"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="7"/>
+      <c r="M1" s="7"/>
+      <c r="N1" s="8"/>
+      <c r="O1" s="9"/>
       <c r="P1"/>
       <c r="Q1"/>
       <c r="R1"/>
@@ -1190,7 +1205,7 @@
       <c r="AI1"/>
       <c r="AJ1"/>
     </row>
-    <row r="2" s="3" customFormat="1" spans="1:36">
+    <row r="2" s="5" customFormat="1" spans="1:36">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1205,9 +1220,9 @@
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="8"/>
-      <c r="O2" s="7"/>
+      <c r="M2" s="7"/>
+      <c r="N2" s="10"/>
+      <c r="O2" s="9"/>
       <c r="P2"/>
       <c r="Q2"/>
       <c r="R2"/>
@@ -1230,7 +1245,7 @@
       <c r="AI2"/>
       <c r="AJ2"/>
     </row>
-    <row r="3" s="4" customFormat="1" spans="1:36">
+    <row r="3" s="6" customFormat="1" spans="1:36">
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
@@ -1249,11 +1264,11 @@
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
-      <c r="K3" s="9"/>
+      <c r="K3" s="11"/>
       <c r="L3" s="2"/>
-      <c r="M3" s="10"/>
-      <c r="N3" s="11"/>
-      <c r="O3" s="7"/>
+      <c r="M3" s="12"/>
+      <c r="N3" s="13"/>
+      <c r="O3" s="9"/>
       <c r="P3"/>
       <c r="Q3"/>
       <c r="R3"/>
@@ -1276,7 +1291,7 @@
       <c r="AI3"/>
       <c r="AJ3"/>
     </row>
-    <row r="4" s="4" customFormat="1" spans="1:36">
+    <row r="4" s="6" customFormat="1" spans="1:36">
       <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
@@ -1289,11 +1304,11 @@
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
-      <c r="K4" s="9"/>
+      <c r="K4" s="11"/>
       <c r="L4" s="2"/>
-      <c r="M4" s="10"/>
-      <c r="N4" s="11"/>
-      <c r="O4" s="7"/>
+      <c r="M4" s="12"/>
+      <c r="N4" s="13"/>
+      <c r="O4" s="9"/>
       <c r="P4"/>
       <c r="Q4"/>
       <c r="R4"/>
@@ -1316,7 +1331,7 @@
       <c r="AI4"/>
       <c r="AJ4"/>
     </row>
-    <row r="5" s="3" customFormat="1" spans="1:36">
+    <row r="5" s="5" customFormat="1" spans="1:36">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
@@ -1335,11 +1350,11 @@
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
-      <c r="K5" s="8"/>
+      <c r="K5" s="10"/>
       <c r="L5" s="1"/>
-      <c r="M5" s="8"/>
+      <c r="M5" s="10"/>
       <c r="N5" s="1"/>
-      <c r="O5" s="7"/>
+      <c r="O5" s="9"/>
       <c r="P5"/>
       <c r="Q5"/>
       <c r="R5"/>
@@ -1372,11 +1387,11 @@
       <c r="D6" t="s">
         <v>13</v>
       </c>
-      <c r="H6" s="12"/>
-      <c r="J6" s="12"/>
-      <c r="L6" s="12"/>
-      <c r="M6" s="13"/>
-      <c r="N6" s="13"/>
+      <c r="H6" s="3"/>
+      <c r="J6" s="3"/>
+      <c r="L6" s="3"/>
+      <c r="M6" s="4"/>
+      <c r="N6" s="4"/>
     </row>
     <row r="7" spans="1:36">
       <c r="B7">
@@ -1388,11 +1403,11 @@
       <c r="D7" t="s">
         <v>15</v>
       </c>
-      <c r="H7" s="12"/>
-      <c r="J7" s="12"/>
-      <c r="L7" s="12"/>
-      <c r="M7" s="13"/>
-      <c r="N7" s="13"/>
+      <c r="H7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="4"/>
+      <c r="N7" s="4"/>
     </row>
     <row r="8" spans="1:36">
       <c r="B8">
@@ -1404,11 +1419,11 @@
       <c r="D8" t="s">
         <v>17</v>
       </c>
-      <c r="H8" s="12"/>
-      <c r="J8" s="12"/>
-      <c r="L8" s="12"/>
-      <c r="M8" s="13"/>
-      <c r="N8" s="13"/>
+      <c r="H8" s="3"/>
+      <c r="J8" s="3"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="4"/>
+      <c r="N8" s="4"/>
     </row>
     <row r="9" spans="1:36">
       <c r="B9">
@@ -1420,63 +1435,79 @@
       <c r="D9" t="s">
         <v>19</v>
       </c>
-      <c r="H9" s="12"/>
-      <c r="J9" s="12"/>
-      <c r="L9" s="12"/>
-      <c r="M9" s="13"/>
-      <c r="N9" s="13"/>
+      <c r="H9" s="3"/>
+      <c r="J9" s="3"/>
+      <c r="L9" s="3"/>
+      <c r="M9" s="4"/>
+      <c r="N9" s="4"/>
     </row>
     <row r="10" spans="1:36">
-      <c r="H10" s="12"/>
-      <c r="J10" s="12"/>
-      <c r="L10" s="12"/>
-      <c r="M10" s="13"/>
-      <c r="N10" s="13"/>
+      <c r="B10">
+        <v>5</v>
+      </c>
+      <c r="C10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" t="s">
+        <v>21</v>
+      </c>
+      <c r="H10" s="3"/>
+      <c r="J10" s="3"/>
+      <c r="L10" s="3"/>
+      <c r="M10" s="4"/>
+      <c r="N10" s="4"/>
     </row>
     <row r="11" spans="1:36">
-      <c r="C11" s="12"/>
-      <c r="H11" s="12"/>
-      <c r="J11" s="12"/>
-      <c r="L11" s="12"/>
-      <c r="M11" s="13"/>
-      <c r="N11" s="13"/>
+      <c r="H11" s="3"/>
+      <c r="J11" s="3"/>
+      <c r="L11" s="3"/>
+      <c r="M11" s="4"/>
+      <c r="N11" s="4"/>
     </row>
     <row r="12" spans="1:36">
-      <c r="H12" s="12"/>
-      <c r="J12" s="12"/>
-      <c r="L12" s="12"/>
-      <c r="M12" s="13"/>
-      <c r="N12" s="13"/>
+      <c r="C12" s="3"/>
+      <c r="H12" s="3"/>
+      <c r="J12" s="3"/>
+      <c r="L12" s="3"/>
+      <c r="M12" s="4"/>
+      <c r="N12" s="4"/>
     </row>
     <row r="13" spans="1:36">
-      <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12"/>
-      <c r="H13" s="14"/>
-      <c r="J13" s="12"/>
-      <c r="L13" s="12"/>
-      <c r="M13" s="13"/>
-      <c r="N13" s="13"/>
+      <c r="H13" s="3"/>
+      <c r="J13" s="3"/>
+      <c r="L13" s="3"/>
+      <c r="M13" s="4"/>
+      <c r="N13" s="4"/>
     </row>
     <row r="14" spans="1:36">
-      <c r="C14" s="12"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
       <c r="H14" s="14"/>
-      <c r="J14" s="12"/>
-      <c r="L14" s="12"/>
-      <c r="M14" s="13"/>
-      <c r="N14" s="13"/>
+      <c r="J14" s="3"/>
+      <c r="L14" s="3"/>
+      <c r="M14" s="4"/>
+      <c r="N14" s="4"/>
     </row>
     <row r="15" spans="1:36">
-      <c r="C15" s="12"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="12"/>
-      <c r="H15" s="12"/>
-      <c r="J15" s="12"/>
-      <c r="L15" s="12"/>
-      <c r="M15" s="13"/>
-      <c r="N15" s="13"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="H15" s="14"/>
+      <c r="J15" s="3"/>
+      <c r="L15" s="3"/>
+      <c r="M15" s="4"/>
+      <c r="N15" s="4"/>
+    </row>
+    <row r="16" spans="1:36">
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="H16" s="3"/>
+      <c r="J16" s="3"/>
+      <c r="L16" s="3"/>
+      <c r="M16" s="4"/>
+      <c r="N16" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1492,13 +1523,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultColWidth="15.1666666666667" defaultRowHeight="14" outlineLevelRow="6" outlineLevelCol="3"/>
+  <dimension ref="A1:N10"/>
+  <sheetFormatPr defaultColWidth="15.1666666666667" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="16384" width="15.1666666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1512,7 +1543,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:14">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1520,7 +1551,7 @@
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:14">
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
@@ -1534,7 +1565,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:14">
       <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
@@ -1542,7 +1573,7 @@
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:14">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
@@ -1556,7 +1587,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" customFormat="1" spans="1:14">
       <c r="B6">
         <v>1</v>
       </c>
@@ -1564,10 +1595,15 @@
         <v>12</v>
       </c>
       <c r="D6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
+        <v>22</v>
+      </c>
+      <c r="H6" s="3"/>
+      <c r="J6" s="3"/>
+      <c r="L6" s="3"/>
+      <c r="M6" s="4"/>
+      <c r="N6" s="4"/>
+    </row>
+    <row r="7" customFormat="1" spans="1:14">
       <c r="B7">
         <v>2</v>
       </c>
@@ -1575,8 +1611,61 @@
         <v>14</v>
       </c>
       <c r="D7" t="s">
-        <v>21</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="H7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="4"/>
+      <c r="N7" s="4"/>
+    </row>
+    <row r="8" customFormat="1" spans="1:14">
+      <c r="B8">
+        <v>3</v>
+      </c>
+      <c r="C8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" t="s">
+        <v>24</v>
+      </c>
+      <c r="H8" s="3"/>
+      <c r="J8" s="3"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="4"/>
+      <c r="N8" s="4"/>
+    </row>
+    <row r="9" customFormat="1" spans="1:14">
+      <c r="B9">
+        <v>4</v>
+      </c>
+      <c r="C9" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" t="s">
+        <v>25</v>
+      </c>
+      <c r="H9" s="3"/>
+      <c r="J9" s="3"/>
+      <c r="L9" s="3"/>
+      <c r="M9" s="4"/>
+      <c r="N9" s="4"/>
+    </row>
+    <row r="10" customFormat="1" spans="1:14">
+      <c r="B10">
+        <v>5</v>
+      </c>
+      <c r="C10" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" t="s">
+        <v>26</v>
+      </c>
+      <c r="H10" s="3"/>
+      <c r="J10" s="3"/>
+      <c r="L10" s="3"/>
+      <c r="M10" s="4"/>
+      <c r="N10" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
